--- a/data/trans_orig/POLIPATOLOGIA_2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/POLIPATOLOGIA_2-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas en 2007</t>
+          <t>Población con dos o más enfermedades crónicas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>371782</t>
+          <t>370294</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>432060</t>
+          <t>430870</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>693287</t>
+          <t>694486</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>765645</t>
+          <t>765954</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1079418</t>
+          <t>1084399</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1176506</t>
+          <t>1179153</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>50,24%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>599663</t>
+          <t>600853</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>659941</t>
+          <t>661429</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>549468</t>
+          <t>549159</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>621826</t>
+          <t>620627</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1170329</t>
+          <t>1167682</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1267417</t>
+          <t>1262436</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>53,79%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>160300</t>
+          <t>158955</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>212534</t>
+          <t>214108</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>284909</t>
+          <t>281980</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>346256</t>
+          <t>343759</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>460382</t>
+          <t>458113</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>539897</t>
+          <t>541818</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,51%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1480879</t>
+          <t>1479305</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1533113</t>
+          <t>1534458</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1241417</t>
+          <t>1243914</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1302764</t>
+          <t>1305693</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2741189</t>
+          <t>2739268</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2820704</t>
+          <t>2822973</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>86,04%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46862</t>
+          <t>47383</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>78384</t>
+          <t>80424</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>73045</t>
+          <t>72617</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>106265</t>
+          <t>107652</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>127859</t>
+          <t>128618</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>175185</t>
+          <t>175967</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,12%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>473024</t>
+          <t>470984</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>504546</t>
+          <t>504025</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>370147</t>
+          <t>368760</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>403367</t>
+          <t>403795</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>77,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>852635</t>
+          <t>851853</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>899961</t>
+          <t>899202</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,49%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>602418</t>
+          <t>604686</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>688582</t>
+          <t>692536</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1079246</t>
+          <t>1079368</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1194125</t>
+          <t>1189882</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1699278</t>
+          <t>1710286</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1855089</t>
+          <t>1847148</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,75%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2587961</t>
+          <t>2584007</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2674125</t>
+          <t>2671857</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2185072</t>
+          <t>2189315</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2299951</t>
+          <t>2299829</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4800652</t>
+          <t>4808593</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4956463</t>
+          <t>4945455</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>74,3%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas en 2012</t>
+          <t>Población con dos o más enfermedades crónicas en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>444012</t>
+          <t>446583</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>508121</t>
+          <t>511922</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>813158</t>
+          <t>811170</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>886050</t>
+          <t>885068</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1276419</t>
+          <t>1278564</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1371811</t>
+          <t>1375492</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,48%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>466522</t>
+          <t>462721</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>530631</t>
+          <t>528060</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>451747</t>
+          <t>452729</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>524639</t>
+          <t>526627</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>940629</t>
+          <t>936948</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1036021</t>
+          <t>1033876</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,71%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>270066</t>
+          <t>270809</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>337562</t>
+          <t>338594</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>396766</t>
+          <t>395044</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>471962</t>
+          <t>474183</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>684848</t>
+          <t>686788</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>786434</t>
+          <t>791588</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,27%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1626395</t>
+          <t>1625363</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1693891</t>
+          <t>1693148</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1285841</t>
+          <t>1283620</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1361037</t>
+          <t>1362759</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2935326</t>
+          <t>2930172</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3036912</t>
+          <t>3034972</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,55%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40760</t>
+          <t>39730</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>71740</t>
+          <t>70454</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>74019</t>
+          <t>75577</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>111193</t>
+          <t>110926</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>123990</t>
+          <t>121740</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>170930</t>
+          <t>168358</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>17,91%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>409441</t>
+          <t>410727</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>440421</t>
+          <t>441451</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>347438</t>
+          <t>347705</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>384612</t>
+          <t>383054</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>768883</t>
+          <t>771455</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>815823</t>
+          <t>818073</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>87,05%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>778256</t>
+          <t>783879</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>888866</t>
+          <t>882909</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1320077</t>
+          <t>1315643</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1434937</t>
+          <t>1437518</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2129203</t>
+          <t>2128959</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2289239</t>
+          <t>2281911</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,72%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2530916</t>
+          <t>2536873</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2641526</t>
+          <t>2635903</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2119293</t>
+          <t>2116712</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2234153</t>
+          <t>2238587</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4684773</t>
+          <t>4692101</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4844809</t>
+          <t>4845053</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas en 2016</t>
+          <t>Población con dos o más enfermedades crónicas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>308165</t>
+          <t>307574</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>362965</t>
+          <t>363759</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>598904</t>
+          <t>600990</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>663046</t>
+          <t>663776</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>925109</t>
+          <t>925324</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1011150</t>
+          <t>1010318</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>57,77%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>391382</t>
+          <t>390588</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>446182</t>
+          <t>446773</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>331614</t>
+          <t>330884</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>395756</t>
+          <t>393670</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>737857</t>
+          <t>738689</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>823898</t>
+          <t>823683</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>47,09%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>339502</t>
+          <t>340743</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>411085</t>
+          <t>411157</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>492820</t>
+          <t>495794</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>577707</t>
+          <t>574490</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>851740</t>
+          <t>855752</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>963412</t>
+          <t>960085</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,62%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1665300</t>
+          <t>1665228</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1736883</t>
+          <t>1735642</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1410593</t>
+          <t>1413810</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1495480</t>
+          <t>1492506</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3101273</t>
+          <t>3104600</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3212945</t>
+          <t>3208933</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>78,95%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>79784</t>
+          <t>82151</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>119166</t>
+          <t>120646</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>92296</t>
+          <t>89560</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>130092</t>
+          <t>130461</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>181096</t>
+          <t>182917</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>236631</t>
+          <t>234395</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>427720</t>
+          <t>426240</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>467102</t>
+          <t>464735</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>419048</t>
+          <t>418679</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>456844</t>
+          <t>459580</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>859396</t>
+          <t>861632</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>914931</t>
+          <t>913110</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,31%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>755479</t>
+          <t>758655</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>855777</t>
+          <t>859414</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1221856</t>
+          <t>1215228</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1336285</t>
+          <t>1342904</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2000443</t>
+          <t>2008174</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2158337</t>
+          <t>2158669</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,7 +5053,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2521841</t>
+          <t>2518204</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2622139</t>
+          <t>2618963</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2195815</t>
+          <t>2189196</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2310244</t>
+          <t>2316872</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4751381</t>
+          <t>4751049</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4909275</t>
+          <t>4901544</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>70,94%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas en 2023</t>
+          <t>Población con dos o más enfermedades crónicas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>265287</t>
+          <t>263820</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>308386</t>
+          <t>307666</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>527472</t>
+          <t>526718</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>567155</t>
+          <t>565446</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>803518</t>
+          <t>803828</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>863613</t>
+          <t>862241</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>67,87%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>206552</t>
+          <t>207272</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>249651</t>
+          <t>251118</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>188353</t>
+          <t>190062</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>228036</t>
+          <t>228790</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>406833</t>
+          <t>408205</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>466928</t>
+          <t>466618</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,73%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>415467</t>
+          <t>407372</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>678475</t>
+          <t>676699</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>874840</t>
+          <t>884296</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1344193</t>
+          <t>1383074</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1378459</t>
+          <t>1353942</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2074903</t>
+          <t>2022510</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>44,67%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1611852</t>
+          <t>1613628</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1874860</t>
+          <t>1882955</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>893630</t>
+          <t>854749</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1362983</t>
+          <t>1353527</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>60,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2453247</t>
+          <t>2505640</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3149691</t>
+          <t>3174208</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>70,1%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>152292</t>
+          <t>152793</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>197696</t>
+          <t>197762</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>224403</t>
+          <t>223579</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>268726</t>
+          <t>267182</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>388685</t>
+          <t>390703</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>452667</t>
+          <t>454860</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,8%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>448927</t>
+          <t>448861</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>494331</t>
+          <t>493830</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>391737</t>
+          <t>393281</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>436060</t>
+          <t>436884</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>854419</t>
+          <t>852226</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>918401</t>
+          <t>916383</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,26%</t>
+          <t>70,11%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>809446</t>
+          <t>803418</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1154026</t>
+          <t>1148131</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1684013</t>
+          <t>1685329</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2188101</t>
+          <t>2156681</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2580328</t>
+          <t>2597369</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3278130</t>
+          <t>3250946</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>45,75%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2297863</t>
+          <t>2303758</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2642443</t>
+          <t>2648471</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1465693</t>
+          <t>1497113</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1969781</t>
+          <t>1968465</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3827553</t>
+          <t>3854737</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4525355</t>
+          <t>4508314</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>63,45%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/POLIPATOLOGIA_2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/POLIPATOLOGIA_2-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>370294</t>
+          <t>372214</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>430870</t>
+          <t>432871</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>694486</t>
+          <t>693388</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>765954</t>
+          <t>763504</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1084399</t>
+          <t>1082427</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1179153</t>
+          <t>1178353</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>50,21%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>600853</t>
+          <t>598852</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>661429</t>
+          <t>659509</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>549159</t>
+          <t>551609</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>620627</t>
+          <t>621725</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1167682</t>
+          <t>1168482</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1262436</t>
+          <t>1264408</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,88%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>158955</t>
+          <t>165263</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>214108</t>
+          <t>214895</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>281980</t>
+          <t>281886</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>343759</t>
+          <t>348365</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>458113</t>
+          <t>457524</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>541818</t>
+          <t>541485</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,5%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1479305</t>
+          <t>1478518</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1534458</t>
+          <t>1528150</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1243914</t>
+          <t>1239308</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1305693</t>
+          <t>1305787</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2739268</t>
+          <t>2739601</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2822973</t>
+          <t>2823562</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,06%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47383</t>
+          <t>47295</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80424</t>
+          <t>77629</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72617</t>
+          <t>70279</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>107652</t>
+          <t>107070</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>128618</t>
+          <t>128242</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>175967</t>
+          <t>176349</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,16%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>470984</t>
+          <t>473779</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>504025</t>
+          <t>504113</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>368760</t>
+          <t>369342</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>403795</t>
+          <t>406133</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>851853</t>
+          <t>851471</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>899202</t>
+          <t>899578</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,52%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>604686</t>
+          <t>602391</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>692536</t>
+          <t>693201</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1079368</t>
+          <t>1078673</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1189882</t>
+          <t>1189146</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1710286</t>
+          <t>1711947</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1847148</t>
+          <t>1860969</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,96%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2584007</t>
+          <t>2583342</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2671857</t>
+          <t>2674152</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2189315</t>
+          <t>2190051</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2299829</t>
+          <t>2300524</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4808593</t>
+          <t>4794772</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4945455</t>
+          <t>4943794</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,28%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>446583</t>
+          <t>447483</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>511922</t>
+          <t>508518</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>811170</t>
+          <t>814821</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>885068</t>
+          <t>883076</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>66,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1278564</t>
+          <t>1274868</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1375492</t>
+          <t>1373447</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,39%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>462721</t>
+          <t>466125</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>528060</t>
+          <t>527160</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>452729</t>
+          <t>454721</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>526627</t>
+          <t>522976</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>936948</t>
+          <t>938993</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1033876</t>
+          <t>1037572</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>44,87%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>270809</t>
+          <t>272575</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>338594</t>
+          <t>335260</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>395044</t>
+          <t>400653</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>474183</t>
+          <t>473051</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>686788</t>
+          <t>690848</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>791588</t>
+          <t>790947</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,25%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1625363</t>
+          <t>1628697</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1693148</t>
+          <t>1691382</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1283620</t>
+          <t>1284752</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1362759</t>
+          <t>1357150</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2930172</t>
+          <t>2930813</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3034972</t>
+          <t>3030912</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,44%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39730</t>
+          <t>40289</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>70454</t>
+          <t>71460</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75577</t>
+          <t>75753</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>110926</t>
+          <t>109855</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>121740</t>
+          <t>123210</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>168358</t>
+          <t>168807</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,96%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>410727</t>
+          <t>409721</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>441451</t>
+          <t>440892</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>347705</t>
+          <t>348776</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>383054</t>
+          <t>382878</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>771455</t>
+          <t>771006</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>818073</t>
+          <t>816603</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>86,89%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>783879</t>
+          <t>776197</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>882909</t>
+          <t>884381</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1315643</t>
+          <t>1317777</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1437518</t>
+          <t>1431580</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2128959</t>
+          <t>2126459</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2281911</t>
+          <t>2285886</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,78%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2536873</t>
+          <t>2535401</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2635903</t>
+          <t>2643585</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2116712</t>
+          <t>2122650</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2238587</t>
+          <t>2236453</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4692101</t>
+          <t>4688126</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4845053</t>
+          <t>4847553</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>69,51%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>307574</t>
+          <t>305462</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>363759</t>
+          <t>359831</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>600990</t>
+          <t>602467</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>663776</t>
+          <t>661897</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>66,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>925324</t>
+          <t>921901</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1010318</t>
+          <t>1006813</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>57,56%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>390588</t>
+          <t>394516</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>446773</t>
+          <t>448885</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>52,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>330884</t>
+          <t>332763</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>393670</t>
+          <t>392193</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>738689</t>
+          <t>742194</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>823683</t>
+          <t>827106</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>47,29%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>340743</t>
+          <t>341362</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>411157</t>
+          <t>412747</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>495794</t>
+          <t>494226</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>574490</t>
+          <t>579372</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>855752</t>
+          <t>854559</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>960085</t>
+          <t>965439</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,75%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1665228</t>
+          <t>1663638</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1735642</t>
+          <t>1735023</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1413810</t>
+          <t>1408928</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1492506</t>
+          <t>1494074</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3104600</t>
+          <t>3099246</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3208933</t>
+          <t>3210126</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>78,98%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82151</t>
+          <t>81394</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>120646</t>
+          <t>120369</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>89560</t>
+          <t>90680</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>130461</t>
+          <t>130542</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>182917</t>
+          <t>180633</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>234395</t>
+          <t>239189</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,82%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>426240</t>
+          <t>426517</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>464735</t>
+          <t>465492</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>418679</t>
+          <t>418598</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>459580</t>
+          <t>458460</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>861632</t>
+          <t>856838</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>913110</t>
+          <t>915394</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>83,52%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>758655</t>
+          <t>761084</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>859414</t>
+          <t>860485</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1215228</t>
+          <t>1216286</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1342904</t>
+          <t>1335416</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2008174</t>
+          <t>2005432</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2158669</t>
+          <t>2158878</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,7 +5053,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2518204</t>
+          <t>2517133</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2618963</t>
+          <t>2616534</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2189196</t>
+          <t>2196684</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2316872</t>
+          <t>2315814</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4751049</t>
+          <t>4750840</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4901544</t>
+          <t>4904286</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>70,98%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>287549</t>
+          <t>305653</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>263820</t>
+          <t>282519</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>307666</t>
+          <t>329509</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>546991</t>
+          <t>590605</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>526718</t>
+          <t>567871</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>565446</t>
+          <t>610586</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>834541</t>
+          <t>896258</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>803828</t>
+          <t>860973</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>862241</t>
+          <t>927801</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>66,24%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>227389</t>
+          <t>272876</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>207272</t>
+          <t>249020</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>251118</t>
+          <t>296010</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>208517</t>
+          <t>231433</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>190062</t>
+          <t>211452</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>228790</t>
+          <t>254167</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>435905</t>
+          <t>504309</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>408205</t>
+          <t>472766</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>466618</t>
+          <t>539594</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>38,53%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>588020</t>
+          <t>633466</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>407372</t>
+          <t>589525</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>676699</t>
+          <t>678858</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1035067</t>
+          <t>854181</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>884296</t>
+          <t>813518</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1383074</t>
+          <t>893028</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1623087</t>
+          <t>1487647</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1353942</t>
+          <t>1430736</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2022510</t>
+          <t>1556291</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>35,35%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1702307</t>
+          <t>1597100</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1613628</t>
+          <t>1551708</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1882955</t>
+          <t>1641041</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>71,6%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1202756</t>
+          <t>1317211</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>854749</t>
+          <t>1278364</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1353527</t>
+          <t>1357874</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2905063</t>
+          <t>2914312</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2505640</t>
+          <t>2845668</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3174208</t>
+          <t>2971223</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>67,5%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>174945</t>
+          <t>196570</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>152793</t>
+          <t>169012</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>197762</t>
+          <t>218936</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>246082</t>
+          <t>274848</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>223579</t>
+          <t>251512</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>267182</t>
+          <t>295836</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>421027</t>
+          <t>471418</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>390703</t>
+          <t>438251</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>454860</t>
+          <t>508910</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>35,18%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>471678</t>
+          <t>515017</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>448861</t>
+          <t>492651</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>493830</t>
+          <t>542575</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>69,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>414381</t>
+          <t>460029</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>393281</t>
+          <t>439041</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>436884</t>
+          <t>483365</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>886059</t>
+          <t>975046</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>852226</t>
+          <t>937554</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>916383</t>
+          <t>1008213</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>69,7%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1050515</t>
+          <t>1135689</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>803418</t>
+          <t>1072769</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1148131</t>
+          <t>1190210</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1828140</t>
+          <t>1719633</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1685329</t>
+          <t>1668737</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2156681</t>
+          <t>1774342</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2878655</t>
+          <t>2855322</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2597369</t>
+          <t>2772301</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3250946</t>
+          <t>2936634</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
+          <t>39,39%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>38,24%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>40,51%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>36,55%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>45,75%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2401374</t>
+          <t>2384994</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2303758</t>
+          <t>2330473</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2648471</t>
+          <t>2447914</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>67,74%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1825654</t>
+          <t>2008674</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1497113</t>
+          <t>1953965</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1968465</t>
+          <t>2059570</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>4227028</t>
+          <t>4393668</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3854737</t>
+          <t>4312356</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4508314</t>
+          <t>4476689</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
+          <t>60,61%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>59,49%</t>
         </is>
       </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>54,25%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>61,76%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
